--- a/src/attributions/attributions_ig_traj_448.xlsx
+++ b/src/attributions/attributions_ig_traj_448.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.06157625662724026</v>
+        <v>-0.05757285795468116</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5644501087041566</v>
+        <v>0.06539142371301677</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,25 +1580,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08694139527071784</v>
+        <v>0.03115514010885569</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1216112570057942</v>
+        <v>-0.05502049653256891</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5491443245379437</v>
+        <v>0.1208996782061297</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1355687296766043</v>
+        <v>0.01152293313655319</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1622,79 +1622,79 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0536333022918455</v>
+        <v>0.01826397058916863</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3002640523613211</v>
+        <v>0.02285085230513808</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3337129035075903</v>
+        <v>-0.003286442598191126</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1601902613830842</v>
+        <v>0.0125286098061692</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1960427520269183</v>
+        <v>0.01213805406984279</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.2333231897710611</v>
+        <v>-0.03675422365613458</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.1152840285931514</v>
+        <v>-0.01934106820794393</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1817539208135134</v>
+        <v>0.03462889396523613</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.142478541566331</v>
+        <v>0.03314352554669659</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
         <v>-0</v>
@@ -1703,25 +1703,25 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.07275988669018189</v>
+        <v>-0.04387393783163714</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.8087004303775692</v>
+        <v>0.2022880117098454</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4949979815533078</v>
+        <v>-0.03384738518297602</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
@@ -1730,10 +1730,10 @@
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0182179697787901</v>
+        <v>-0.03182350365143033</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.03985558845208506</v>
+        <v>-0.02284111718973127</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,40 +1742,40 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.2302974974118596</v>
+        <v>-0.009080079176720914</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.01736736983066244</v>
+        <v>0.01297798226846951</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1438997686973183</v>
+        <v>0.06882895055890303</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.169317199136851</v>
+        <v>0.03864898395751101</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,103 +1784,103 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.07128635021337223</v>
+        <v>0.003514938255527361</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.4326706536690318</v>
+        <v>0.1379872482716609</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2319054719852899</v>
+        <v>0.03552165225702267</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.005577095920974423</v>
+        <v>0.02399493813455909</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.2391132965217062</v>
+        <v>-0.04260863495998971</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.01966243981919247</v>
+        <v>-0.02205606839484575</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.1500109630489651</v>
+        <v>-0.02419691407854167</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.03450646788689741</v>
+        <v>-0.08052528120222771</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2258093079942325</v>
+        <v>-0.0202073569892197</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.004572385870167298</v>
+        <v>0.008766901901440236</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.2460990710162006</v>
+        <v>-0.04131766847665394</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.02186019571078159</v>
+        <v>-0.04298613650118183</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
@@ -1892,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.02871426572657681</v>
+        <v>-0.0009465078310492446</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.1729307579225279</v>
+        <v>-0.05665574627051396</v>
       </c>
       <c r="DG3" t="n">
         <v>-0</v>
@@ -1904,34 +1904,34 @@
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.04954100520795113</v>
+        <v>-0.04962471738575576</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.05419797970864702</v>
+        <v>-0.01099200340648476</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.1204384242310453</v>
+        <v>0.009408460448573274</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.1551699300234854</v>
+        <v>-0.01827085626508633</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1940,55 +1940,55 @@
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.01459797722949796</v>
+        <v>0.04151724233969208</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.3075748980504927</v>
+        <v>-0.07407009797905773</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.05160747350197604</v>
+        <v>-0.04912066795949805</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.03250237987252422</v>
+        <v>0.004652009681854371</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.09999737877382915</v>
+        <v>0.008932042474530312</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.1355628779912084</v>
+        <v>-0.03904474878859285</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
@@ -2000,37 +2000,37 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.005958738348511286</v>
+        <v>0.005253625832917724</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.2654285383757937</v>
+        <v>-0.02196754513866024</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.06736087727164236</v>
+        <v>-0.02971135600487992</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.04665858150971016</v>
+        <v>0.01597797369279857</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.2651695771882489</v>
+        <v>-0.06340211435419592</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
@@ -2039,25 +2039,25 @@
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.04901002784469745</v>
+        <v>-0.04224603540951543</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.03689905729257257</v>
+        <v>0.0002224633211432474</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.0734951836973152</v>
+        <v>0.03864917694155075</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
@@ -2066,10 +2066,10 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.0748368957775964</v>
+        <v>-0.006657324687371767</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2078,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.07394288924975767</v>
+        <v>0.07154704807868942</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.2240361187519963</v>
+        <v>-0.04022713007662164</v>
       </c>
       <c r="FR3" t="n">
         <v>-0</v>
@@ -2093,13 +2093,13 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.1352124642726351</v>
+        <v>0.05027694015479655</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
         <v>-0</v>
@@ -2108,31 +2108,31 @@
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.1380909247310741</v>
+        <v>0.03188769966526104</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.1343931660454377</v>
+        <v>-0.0232991288832371</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2709,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4664181600281113</v>
+        <v>0.4682853429015372</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1215801486489472</v>
+        <v>-0.2381159881712207</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01118516738148109</v>
+        <v>-0.04972803024051873</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
@@ -2736,184 +2736,184 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3663772425422845</v>
+        <v>0.4971981777671003</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.192119930455531</v>
+        <v>-0.436097792747844</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06883368743581604</v>
+        <v>-0.1501091402983857</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1810060130624193</v>
+        <v>0.2060217859693301</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0009711015904963288</v>
+        <v>-0.02351049913893091</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05934406775138831</v>
+        <v>0.01347979951389169</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1480502544904574</v>
+        <v>-0.164585846683023</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.02204142983428598</v>
+        <v>-0.3553688763396161</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.05043152116222669</v>
+        <v>-0.151977767479601</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02026158519963714</v>
+        <v>0.2313059300216181</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.1005185086958257</v>
+        <v>-0.09545933318367938</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.08711789924766952</v>
+        <v>0.1679965977026505</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5034689717205131</v>
+        <v>0.58833699002814</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.009442294190010404</v>
+        <v>-0.2827208973652678</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2451817067021604</v>
+        <v>-0.4232668297757521</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.07022810203517374</v>
+        <v>0.06961852200271638</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.09535246756986654</v>
+        <v>-0.126898988577586</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.144902088929586</v>
+        <v>-0.02359128826844687</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0547674195590135</v>
+        <v>-0.04622332414972151</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.752852295790391e-10</v>
+        <v>7.170001804452538e-11</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.2274649136150749</v>
+        <v>-0.02414149162544564</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,52 +2922,52 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2594452133519254</v>
+        <v>0.566410002802166</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.01856581642885704</v>
+        <v>-0.1950999685551371</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0850269006658953</v>
+        <v>-0.05429359100086253</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.156680037834148</v>
+        <v>-0.2082208294654647</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01340834207470878</v>
+        <v>0.2234595916125201</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02876772843215744</v>
+        <v>-0.00783429423435163</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0009603401562005243</v>
+        <v>-0.2342571216630094</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.1023825971240279</v>
+        <v>0.2643177356169402</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1120763919394431</v>
+        <v>0.1082242209007168</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1504955811149828</v>
+        <v>-0.219608170671326</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.04677980831838446</v>
+        <v>0.2353698139426215</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.03436534377897992</v>
+        <v>-0.004001439046444907</v>
       </c>
       <c r="DA5" t="n">
         <v>-0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
@@ -3033,16 +3033,16 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1073550004225386</v>
+        <v>-0.2380646588873963</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.005697320507107386</v>
+        <v>0.2264400537771155</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.03554451963310035</v>
+        <v>-0.007266978059834393</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
@@ -3054,49 +3054,49 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.03797971118016058</v>
+        <v>-0.06012274326642877</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.1445774651546949</v>
+        <v>0.08233639063075981</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.03150022683943575</v>
+        <v>0.06813644933348879</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.108900792689901</v>
+        <v>0.05242075103807404</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.008170735236127543</v>
+        <v>0.1415752221116317</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.02032169238787765</v>
+        <v>-0.07023090534010594</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
@@ -3105,58 +3105,58 @@
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1096274630900833</v>
+        <v>-0.1515405758365064</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.01860708434370387</v>
+        <v>0.1867316009151211</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.06626430637458251</v>
+        <v>0.006638200622941502</v>
       </c>
       <c r="EK5" t="n">
         <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1467796459344186</v>
+        <v>-0.1970955188984889</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.1123335465429344</v>
+        <v>-0.1357634455757077</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.09221073772366843</v>
+        <v>-0.1308150664415143</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1574689103804651</v>
+        <v>-0.2505668362795047</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.009687043752907496</v>
+        <v>0.2665274482653393</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02997147279199384</v>
+        <v>-0.02946683077463004</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
@@ -3195,79 +3195,79 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.003141642695163175</v>
+        <v>-0.1716977165107767</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.06948637788492454</v>
+        <v>0.1332038549593061</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.001308650172979257</v>
+        <v>-0.04438156937888483</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.009177169448195244</v>
+        <v>-0.1267482438138032</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0526221200789896</v>
+        <v>0.2590133444405026</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.06605812252549827</v>
+        <v>0.3792907548636875</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.01449753626028855</v>
+        <v>-0.2053923220485646</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.08897468858946508</v>
+        <v>0.09577273319669485</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,25 +3275,25 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.1954220276477008</v>
+        <v>-0.0103160681632084</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4187980472901455</v>
+        <v>0.03104733371328024</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1427876999395904</v>
+        <v>-0.00633632570122907</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3302,25 +3302,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1642856331673168</v>
+        <v>-0.009457481675768788</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3955840716517784</v>
+        <v>0.04361552811704669</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2459164298240328</v>
+        <v>-0.01160713554406009</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,79 +3329,79 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009607558461566086</v>
+        <v>0.008769075044715904</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2763618112284098</v>
+        <v>0.007997785411680157</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1696050801791777</v>
+        <v>-0.003061375810240908</v>
       </c>
       <c r="X6" t="n">
         <v>-0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1354307849188243</v>
+        <v>0.001648734241318658</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2947873128072957</v>
+        <v>-0.001088552879120609</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.00410490926154863</v>
+        <v>-0.0007682189970629684</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.02370499003951426</v>
+        <v>-0.001905791187922055</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1849425574617186</v>
+        <v>0.014228853726943</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.09931945016272162</v>
+        <v>0.006072550568035824</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.02089235232621242</v>
+        <v>-0.004397166557826631</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4534230801292248</v>
+        <v>0.03652424763107083</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,7 +3422,7 @@
         <v>-0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2879339082676228</v>
+        <v>-0.01086084438109748</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -3431,16 +3431,16 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.08157788323026539</v>
+        <v>-0.008254385275492635</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.02057230282866103</v>
+        <v>0.002292252182122637</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,40 +3449,40 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.2921517255692092</v>
+        <v>-0.003877497816722388</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.06693964291718139</v>
+        <v>-0.004524402500527982</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1619538659553889</v>
+        <v>0.001158724834920228</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02592736573383759</v>
+        <v>0.02512127233332487</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3491,19 +3491,19 @@
         <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.03262968612934</v>
+        <v>0.004227351839267425</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.3619661304040587</v>
+        <v>0.03303276482803682</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.08308823617608486</v>
+        <v>-0.0007358583059341551</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -3518,10 +3518,10 @@
         <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.05590909230270501</v>
+        <v>0.004346253237610816</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.131510401549352</v>
+        <v>-0.01302871114541151</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,25 +3530,25 @@
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.008436180995150261</v>
+        <v>0.003703425327250261</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
         <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.08512089582025675</v>
+        <v>-0.001528489332836544</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0003671429667994622</v>
+        <v>-0.0149747729435549</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1372253758997457</v>
+        <v>-0.002223287480388758</v>
       </c>
       <c r="CR6" t="n">
         <v>-0</v>
@@ -3569,13 +3569,13 @@
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.03984029655182653</v>
+        <v>0.001880732509645821</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1471517614096199</v>
+        <v>-0.01292255530860309</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.006991832366679</v>
+        <v>0.001447247174050648</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
@@ -3599,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.04474372956995568</v>
+        <v>-0.003844460500089291</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.2044638203474287</v>
+        <v>-0.01200324518366015</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
@@ -3611,25 +3611,25 @@
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05237009733591919</v>
+        <v>-0.002491573088339638</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL6" t="n">
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.05586133783722487</v>
+        <v>-0.002211656035874129</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.06456930078015653</v>
+        <v>-0.01103290956344435</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
@@ -3638,7 +3638,7 @@
         <v>-0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.07789967593555609</v>
+        <v>0.0003506298892161012</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
@@ -3653,10 +3653,10 @@
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.01404735728124516</v>
+        <v>0.01196760532452962</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.1306605936037903</v>
+        <v>0.01265585375023559</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,25 +3665,25 @@
         <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01969679808450326</v>
+        <v>-0.009462154568041706</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.04326456552472081</v>
+        <v>-0.001212921026728375</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.005405376928812179</v>
+        <v>-0.0062737838269038</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
@@ -3692,34 +3692,34 @@
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.01422267724864703</v>
+        <v>-0.005117947919140731</v>
       </c>
       <c r="EK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>-0.03776585529504655</v>
+        <v>-0.001269886608168008</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.1711025048142696</v>
+        <v>9.869023178246072e-05</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
         <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01769306404251002</v>
+        <v>-0.003933714830722043</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
@@ -3728,25 +3728,25 @@
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
         <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.03029612983941903</v>
+        <v>0.003464966610037759</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1563182147413756</v>
+        <v>-0.0155632058468946</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.05871755482127297</v>
+        <v>0.0003284337832154639</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
@@ -3761,10 +3761,10 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.06370083871925934</v>
+        <v>-0.003954452399142477</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.04955302734521723</v>
+        <v>-0.007265135153370665</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,7 +3773,7 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.1261182687378794</v>
+        <v>0.003238924803603266</v>
       </c>
       <c r="FL6" t="n">
         <v>0</v>
@@ -3782,16 +3782,16 @@
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
         <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.02253090324650593</v>
+        <v>0.02795509731640816</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.2489632334103506</v>
+        <v>-0.01650086210211436</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,28 +3800,28 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.1258002471888759</v>
+        <v>0.006681226049556769</v>
       </c>
       <c r="FU6" t="n">
         <v>-0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0.1035946370815953</v>
+        <v>0.003904638178004795</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.009553946874924474</v>
+        <v>-0.01246110924771527</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,16 +3830,16 @@
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,22 +3847,22 @@
         <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5041257075296405</v>
+        <v>0.8568153059684924</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2372310548447105</v>
+        <v>-0.6088767832673969</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1035092374264696</v>
+        <v>-0.2699642678122924</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3874,73 +3874,73 @@
         <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3996329631951012</v>
+        <v>0.8167342105706868</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2819004637376676</v>
+        <v>-1.052859791784266</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1383394914988111</v>
+        <v>-0.4492792173119824</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1606942981272629</v>
+        <v>0.304240280873652</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002691112396589718</v>
+        <v>-0.05006718989462842</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1170613397109735</v>
+        <v>-0.005538513604608591</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1571321381522187</v>
+        <v>0.08769046024882236</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.007017634708715211</v>
+        <v>-0.2611387072385988</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.06580045571954454</v>
+        <v>-0.09523216317336625</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -3952,25 +3952,25 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.07144346506423993</v>
+        <v>0.4969755794466454</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.07869462828334506</v>
+        <v>-0.05581127685421404</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.04617354243856747</v>
+        <v>0.4021372193602003</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.6452813833261344</v>
+        <v>1.138486713305548</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.03043859008565071</v>
+        <v>-0.5041568135802295</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1391167645546309</v>
+        <v>-0.414943357066522</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
         <v>-0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02405989534763088</v>
+        <v>-0.2107864928113584</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1319058621420198</v>
+        <v>-0.05406049057420406</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1807497268309333</v>
+        <v>-0.1651812403897304</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4033,25 +4033,25 @@
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03751516374155741</v>
+        <v>-0.193065397841187</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06208305875132897</v>
+        <v>0.03155619771200846</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.151222827424272</v>
+        <v>0.0949322579786722</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,22 +4063,22 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.3486807137794953</v>
+        <v>0.8624164315412228</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01771006915125703</v>
+        <v>-0.4790741372706121</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.09983602611845714</v>
+        <v>-0.1126969197884213</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>-0</v>
@@ -4087,19 +4087,19 @@
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1413956959969701</v>
+        <v>-0.3795638468566662</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.05561173392831632</v>
+        <v>0.3042602088587234</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02943430999816766</v>
+        <v>0.03037913265803834</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
@@ -4117,16 +4117,16 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02933609226176554</v>
+        <v>-0.2938505078863227</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.08407037218359455</v>
+        <v>0.2308470652944163</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1695380737959747</v>
+        <v>0.120946747963074</v>
       </c>
       <c r="CR7" t="n">
         <v>0</v>
@@ -4141,25 +4141,25 @@
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1274961537618101</v>
+        <v>-0.4162981355750086</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.08103396217414308</v>
+        <v>0.3166390183444463</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02615883410276997</v>
+        <v>0.07870652212981426</v>
       </c>
       <c r="DA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,25 +4171,25 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.127091763715067</v>
+        <v>-0.5422200153834831</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.07403145058595569</v>
+        <v>0.4566849559314103</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.03782592316156227</v>
+        <v>-0.05710051901198329</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>0</v>
@@ -4198,25 +4198,25 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.08871101625336741</v>
+        <v>-0.1891036104746704</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.04223766106366407</v>
+        <v>0.1467244359445068</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.07778481783605634</v>
+        <v>-0.1088823832657208</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,25 +4225,25 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.05302322513064234</v>
+        <v>0.2081769225832359</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.01797153088033895</v>
+        <v>0.2250389877588759</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.0441536828297382</v>
+        <v>-0.09605133837916424</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
@@ -4252,16 +4252,16 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1071656930668131</v>
+        <v>-0.2671420108921718</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0665940028053852</v>
+        <v>0.2418490711621946</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.1405955523304833</v>
+        <v>0.05241920157810362</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
@@ -4270,31 +4270,31 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.0933933088195308</v>
+        <v>-0.3285205620562919</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.1001866333918145</v>
+        <v>0.2426237692551511</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.09258164801621771</v>
+        <v>-0.01201999732360987</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,100 +4306,100 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1389333722460638</v>
+        <v>-0.4547254321710622</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.07461870801245589</v>
+        <v>0.3570042281884021</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03304935999091547</v>
+        <v>0.05577814974903321</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01848347800476622</v>
+        <v>-0.1648020455318656</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.03594897980764319</v>
+        <v>-0.01750351395905918</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01987819567541265</v>
+        <v>0.009890038021058502</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.002018720470150852</v>
+        <v>-0.3977528818043283</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.09899104132610075</v>
+        <v>0.5957534199028282</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.1446575625095987</v>
+        <v>0.1465303927987074</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.0515637035475681</v>
+        <v>-0.3419325735427342</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.042083001003991</v>
+        <v>0.1103618156523428</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1743930348667126</v>
+        <v>0.5559955786001023</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03473326318764297</v>
+        <v>-0.02065415082430114</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1124399238096319</v>
+        <v>-0.2223175223215941</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1376535954122998</v>
+        <v>0.6615410986545812</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,37 +4452,37 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02536916286700803</v>
+        <v>-0.1838555506453356</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1282912440437764</v>
+        <v>-0.2291778061039259</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03083896390262631</v>
+        <v>0.1069058666708219</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.01140347722961424</v>
+        <v>-0.06730897096717951</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.009205706395514775</v>
+        <v>-0.07859132451880435</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
@@ -4497,49 +4497,49 @@
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03044405612371312</v>
+        <v>0.0625074690758185</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01337513956841836</v>
+        <v>-0.2481711766538325</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.02085538396420539</v>
+        <v>-0.08190399740340169</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01841579955003348</v>
+        <v>0.140649309575628</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.008689224508616223</v>
+        <v>0.0391252331223627</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.05519197051151679</v>
+        <v>-0.1324463105333911</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,25 +4548,25 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.147119580441308</v>
+        <v>0.8144819740392418</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.01217970476227227</v>
+        <v>-0.1705805019913505</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1314720237560484</v>
+        <v>-0.1944781170188318</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
         <v>-0</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.06390055733204919</v>
+        <v>-0.02501270214271965</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,40 +4587,40 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.03072026887686052</v>
+        <v>-0.09022327886521363</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.0359304154919657</v>
+        <v>-0.1064794505480946</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04248848834845207</v>
+        <v>0.09036896574245128</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.02194265649991996</v>
+        <v>0.1003846781688467</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.003400706760048903</v>
+        <v>0.04802229830850138</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
@@ -4632,7 +4632,7 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.07789481698900219</v>
+        <v>0.5214031883452266</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.01245385775957143</v>
+        <v>-0.03885382191803766</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.0572230167096204</v>
+        <v>-0.1850077668209492</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4656,82 +4656,82 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.04297514468073706</v>
+        <v>-0.2431073315763615</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-9.446815642010504e-05</v>
+        <v>0.01345866633073804</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03314030280160316</v>
+        <v>0.1428925764393147</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01340257530726127</v>
+        <v>-0.2908919882746134</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.005747351306206976</v>
+        <v>0.09176605520377537</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.008419242035111152</v>
+        <v>0.1359433827834709</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03558843357916609</v>
+        <v>-0.2317642737723573</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.001738572184703807</v>
+        <v>-0.009032074489709397</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.03759876361616611</v>
+        <v>0.1256118302735158</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.03478892179711686</v>
+        <v>-0.07157760703209115</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03966669339468282</v>
+        <v>-0.2507914476189344</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.03437012730037958</v>
+        <v>0.04452735280817086</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,148 +4761,148 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.01120300926004788</v>
+        <v>-0.08352260196753718</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01900164208977507</v>
+        <v>0.02806326577600326</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.006033138519774721</v>
+        <v>0.06643566011771049</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.04375969307372416</v>
+        <v>0.06387392226613219</v>
       </c>
       <c r="DY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.009890927883237912</v>
+        <v>-0.009480443808129652</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.01338624962262904</v>
+        <v>-0.0525611054054545</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.02821440013369807</v>
+        <v>-0.06934428511494549</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0116772456484757</v>
+        <v>-0.07529073852754813</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01614942456304305</v>
+        <v>0.1060761332642933</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.01329620180428465</v>
+        <v>-0.1382410252635656</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.001342134466025575</v>
+        <v>-0.1321696295466365</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.009456040165660524</v>
+        <v>0.04266169099847108</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03715442110182327</v>
+        <v>-0.2549621173132642</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.006034088691866806</v>
+        <v>-0.03269749550219546</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03692217566401769</v>
+        <v>0.1225317659600469</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.006710723855572024</v>
+        <v>-0.2395138761200216</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
@@ -4911,25 +4911,25 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.02678989488238155</v>
+        <v>0.05918547724005845</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.05175248878279542</v>
+        <v>0.1223242585055235</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.0184925737797745</v>
+        <v>-0.2056714585611101</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,10 +4938,10 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.01825478339632675</v>
+        <v>0.004696418540330808</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.004055218709608235</v>
+        <v>0.01217980809621899</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4950,25 +4950,25 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01833227671029344</v>
+        <v>-0.1165456938628772</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.04827680823440983</v>
+        <v>0.005536997938442456</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,81 +4977,81 @@
         <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3283068073820434</v>
+        <v>0.5546852372090938</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1207774283402124</v>
+        <v>-0.2985380014767023</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07773988633430826</v>
+        <v>-0.1168869961924244</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2352662396350179</v>
+        <v>0.5196910088250466</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1411833572811504</v>
+        <v>-0.5546422675327497</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1199824716543887</v>
+        <v>-0.2191071027290926</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08784805924325044</v>
+        <v>0.1195558278104156</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.007117985798446931</v>
+        <v>-0.0276905411857124</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02143947730245838</v>
+        <v>-0.08380614475397584</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
@@ -5060,58 +5060,58 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1014984607774064</v>
+        <v>0.05800741887370368</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02173333987599557</v>
+        <v>-0.1470890499724043</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01354588346448615</v>
+        <v>-0.05062677701335042</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.009392643053794732</v>
+        <v>0.2051118684709757</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.02299711906343939</v>
+        <v>-0.01955091184137735</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.09067660282806821</v>
+        <v>0.07041677504577491</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,22 +5120,22 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.3963180747627342</v>
+        <v>0.5198429610768265</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.04327219128759652</v>
+        <v>-0.313796278250719</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.07798558662555109</v>
+        <v>-0.3671743145871198</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -5144,19 +5144,19 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03279996808661855</v>
+        <v>0.05415309540523554</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.05196272173987439</v>
+        <v>-0.03184878999330819</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1115664831392619</v>
+        <v>0.008304818314128954</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1099654645002262</v>
+        <v>0.05835324803879825</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.02163232906724719</v>
+        <v>0.0527655378216273</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1467288976874444</v>
+        <v>0.1105534878037917</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
@@ -5201,43 +5201,43 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.213174879106405</v>
+        <v>0.3328431024724878</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.005104996168572356</v>
+        <v>-0.2714357280188807</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.04376484871564493</v>
+        <v>-0.1174516939401029</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.08173743051855564</v>
+        <v>-0.1671002776084464</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.02153433136440049</v>
+        <v>0.2159963378973571</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.003563493582222834</v>
+        <v>0.03273409679469978</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
@@ -5255,19 +5255,19 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.04472240024823495</v>
+        <v>-0.1186736643120114</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.04306232508372304</v>
+        <v>0.08319910075339375</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.06629283659070384</v>
+        <v>0.03010460112488755</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,31 +5276,31 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.06531559479077755</v>
+        <v>-0.1793496112642787</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.04057442749354043</v>
+        <v>0.2350890751526966</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.003414956353138951</v>
+        <v>0.03408599927322788</v>
       </c>
       <c r="DA9" t="n">
         <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,19 +5309,19 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.04330229135967675</v>
+        <v>-0.1089648853466072</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1092370631613046</v>
+        <v>0.1394371330391257</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01849228182279138</v>
+        <v>0.008925502100190139</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5336,70 +5336,70 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.05369333703049096</v>
+        <v>-0.1275865391552042</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.08138346781767614</v>
+        <v>0.09946696701086753</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.006022467148449112</v>
+        <v>-0.09838165278752974</v>
       </c>
       <c r="DS9" t="n">
         <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0517965445569347</v>
+        <v>0.03721357081371836</v>
       </c>
       <c r="DY9" t="n">
         <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.006157345703735695</v>
+        <v>0.07760254633513035</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.02980874777856182</v>
+        <v>-0.1026672525740857</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.06100644147310545</v>
+        <v>-0.07173718879720327</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.09302589795709308</v>
+        <v>-0.285709534009936</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.07627301779843605</v>
+        <v>0.01586514428527307</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
@@ -5408,31 +5408,31 @@
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.06157103800492181</v>
+        <v>-0.1365842609927448</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.07403088763190442</v>
+        <v>0.1029680607763892</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.009539076614804168</v>
+        <v>-0.002252424641925565</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5441,28 +5441,28 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.06678389206811626</v>
+        <v>-0.1993174846435619</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.03677232928477695</v>
+        <v>0.2356230456203737</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01268033339422586</v>
+        <v>0.01603500618745539</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
@@ -5471,16 +5471,16 @@
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.04346098200100585</v>
+        <v>-0.05770198306099871</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.02789116306574649</v>
+        <v>0.05537502643849487</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.03958641003710229</v>
+        <v>0.01431367054415188</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5489,28 +5489,28 @@
         <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.03627809883764446</v>
+        <v>-0.2025611335880948</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.00845254374100959</v>
+        <v>0.4155078819496389</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.05696582436926316</v>
+        <v>0.03734316488120809</v>
       </c>
       <c r="FU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5522,28 +5522,28 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.0161496499722509</v>
+        <v>-0.1043012828526444</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.001233148128233219</v>
+        <v>0.05290726086626794</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -5551,25 +5551,25 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.07696947270004473</v>
+        <v>-0.1667935685392538</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2016214502256299</v>
+        <v>0.1014227294883482</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1157869669215288</v>
+        <v>0.03176327599277187</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1033734512647029</v>
+        <v>-0.1316755380446173</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5578,25 +5578,25 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.02210908396022081</v>
+        <v>-0.1872729581279751</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1331561995673929</v>
+        <v>0.04360426503334254</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04318351270748384</v>
+        <v>0.03309026176790266</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1099002715246304</v>
+        <v>-0.2346905634302421</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -5605,25 +5605,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02093336906773674</v>
+        <v>-0.01604690777538398</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06676316770881574</v>
+        <v>-0.07192402929874286</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.07890522887082978</v>
+        <v>-0.1087378855410166</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.04614720424183687</v>
+        <v>0.04136049769668151</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -5632,52 +5632,52 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.01597202117037514</v>
+        <v>0.1795508579032039</v>
       </c>
       <c r="AC10" t="n">
         <v>-0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.06950806967032129</v>
+        <v>-0.06469627547750113</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.03093881280961872</v>
+        <v>-0.1920615000507574</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.00117022905000689</v>
+        <v>-0.01362954519874577</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.01983965001769866</v>
+        <v>-0.04834363525445989</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.04789683462262502</v>
+        <v>0.00626850048220697</v>
       </c>
       <c r="AN10" t="n">
         <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.02366668118632644</v>
+        <v>-0.1603870856647627</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.02286211221197578</v>
+        <v>0.06756104661045517</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5686,187 +5686,187 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.02884374295048727</v>
+        <v>-0.245968604890383</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2193972234743503</v>
+        <v>0.08363011454957177</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3207702557496955</v>
+        <v>-0.2611355096996081</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.07020748774478684</v>
+        <v>-0.07499317923396336</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.06003626100989187</v>
+        <v>0.06914623789447423</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.02691095007386184</v>
+        <v>-0.06382996649540122</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.009544828863084165</v>
+        <v>0.2613721001494581</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0.05976000291450284</v>
+        <v>-0.1525424998493522</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.008113265322946879</v>
+        <v>0.00594925432933783</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.1017514575820282</v>
+        <v>-0.0007917501977417385</v>
       </c>
       <c r="BO10" t="n">
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1244854733840165</v>
+        <v>0.1109281344029072</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0189180233771716</v>
+        <v>0.1085486779526619</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0.01385128518564919</v>
+        <v>-0.07122062529404587</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.06774734881929438</v>
+        <v>0.04436222409309436</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.1902448076776465</v>
+        <v>-0.1251939286486346</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0.02656331894542038</v>
+        <v>0.0111157199646866</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.02034133825941085</v>
+        <v>0.02252828849775495</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF10" t="n">
-        <v>-0.04699263444004738</v>
+        <v>0.008195351633972879</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01668366728162284</v>
+        <v>0.05214375396410041</v>
       </c>
       <c r="CI10" t="n">
         <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.04383616154534201</v>
+        <v>0.06455900505287948</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0.01862564290496641</v>
+        <v>-0.09999721732058417</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.02095571106115168</v>
+        <v>0.0642684124411385</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.09566336127992235</v>
+        <v>-0.07029107536990466</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0.01574613581124839</v>
+        <v>0.01624192016268257</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.008467205444187862</v>
+        <v>0.04128722286851384</v>
       </c>
       <c r="CW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0.04890065092296637</v>
+        <v>-0.02167170888124275</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01159564163286751</v>
+        <v>-0.01737959989113784</v>
       </c>
       <c r="DA10" t="n">
         <v>-0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.05012097697111455</v>
+        <v>0.08908667285410664</v>
       </c>
       <c r="DC10" t="n">
         <v>0</v>
@@ -5875,106 +5875,106 @@
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.06479758714463849</v>
+        <v>0.03923765503348176</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0.05772440718896819</v>
+        <v>-0.05842838898083177</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.003157092802213352</v>
+        <v>0.1589790689536277</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.00679964774954456</v>
+        <v>0.01394559409372529</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0476987066068679</v>
+        <v>-0.1581962272888586</v>
       </c>
       <c r="DO10" t="n">
         <v>-0</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.02668329201269046</v>
+        <v>0.03163933647904523</v>
       </c>
       <c r="DQ10" t="n">
         <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.0548485526824387</v>
+        <v>-0.2161378547556911</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.02249029706572267</v>
+        <v>0.04987440096681796</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.013233896686564</v>
+        <v>0.1458744392883255</v>
       </c>
       <c r="DX10" t="n">
         <v>0</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.05656239692128827</v>
+        <v>0.05352047267319129</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.08500902360990245</v>
+        <v>-0.1134735254906999</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.006723966083309936</v>
+        <v>0.0422995546070046</v>
       </c>
       <c r="ED10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.0215345684281638</v>
+        <v>0.04069027541217526</v>
       </c>
       <c r="EG10" t="n">
         <v>0</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0.1276345191394526</v>
+        <v>-0.0005426594663451406</v>
       </c>
       <c r="EI10" t="n">
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.07436289157042429</v>
+        <v>0.03521348450801894</v>
       </c>
       <c r="EK10" t="n">
         <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.02797119219255734</v>
+        <v>0.1012249384791488</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,136 +5983,136 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.01180000823078715</v>
+        <v>0.1446003899274632</v>
       </c>
       <c r="EP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0.01137635458638876</v>
+        <v>0.05446466221190242</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.05499382572839853</v>
+        <v>-0.02394195822236015</v>
       </c>
       <c r="ET10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0.007606054264812314</v>
+        <v>0.1514079952225036</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01030271888870477</v>
+        <v>0.04172782576377283</v>
       </c>
       <c r="EY10" t="n">
         <v>0</v>
       </c>
       <c r="EZ10" t="n">
-        <v>-0.05062782566597504</v>
+        <v>-0.02197200912166364</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.0150272712597896</v>
+        <v>0.002822113405825621</v>
       </c>
       <c r="FC10" t="n">
         <v>0</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0454164443421159</v>
+        <v>0.05679857242195303</v>
       </c>
       <c r="FE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.04081222778784157</v>
+        <v>0.2391487355526638</v>
       </c>
       <c r="FH10" t="n">
         <v>-0</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.009888464164040838</v>
+        <v>-0.04458954769128614</v>
       </c>
       <c r="FJ10" t="n">
         <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.0275050529342836</v>
+        <v>0.1157313108395128</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0.0463984432806392</v>
+        <v>0.1129971116110604</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.03286563646129265</v>
+        <v>0.2151819542392475</v>
       </c>
       <c r="FQ10" t="n">
         <v>0</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.04409374242748866</v>
+        <v>-0.1206880128472348</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.04757975094221137</v>
+        <v>0.0391215180268468</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.01792633521516845</v>
+        <v>0.1270336469302671</v>
       </c>
       <c r="FW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0.02145652209839058</v>
+        <v>0.06787939152960495</v>
       </c>
       <c r="FZ10" t="n">
         <v>-0</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.01353339181145704</v>
+        <v>-0.01741489497918208</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0.01506458312684127</v>
+        <v>0.0337834174698865</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6123,19 +6123,19 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1652892862556573</v>
+        <v>0.6893016163504453</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0264146024961754</v>
+        <v>0.0632215396782748</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1174356493132239</v>
+        <v>-0.2602504050407031</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6144,58 +6144,58 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1379468754328304</v>
+        <v>0.8769340425582905</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02124926973936801</v>
+        <v>-0.1402134724077641</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1127670127139074</v>
+        <v>-0.2104187901012486</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02404256971153591</v>
+        <v>0.1325919773085968</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.007093590057199175</v>
+        <v>-0.1196830707257678</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.0125614788636972</v>
+        <v>-0.06524569108027665</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,22 +6204,22 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02094900141080212</v>
+        <v>0.05581994072575606</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0159617055140481</v>
+        <v>-0.3243268661452562</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01301831500287388</v>
+        <v>-0.1430175346577346</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.01636867971189054</v>
+        <v>0.16951601968081</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0101043825122123</v>
+        <v>0.005558126822987357</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.04786832545120231</v>
+        <v>-0.1673407906629854</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1164872141931369</v>
+        <v>0.8998527642728276</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
@@ -6267,25 +6267,25 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.004705182197437219</v>
+        <v>-0.2810563383041461</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.08347751699450125</v>
+        <v>-0.25509003650125</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.06265281871981307</v>
+        <v>-0.05991086681008512</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,52 +6294,52 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.04465927375930281</v>
+        <v>-0.08089073757300648</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.04931744919729091</v>
+        <v>-0.1094601132500402</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.03639492417860281</v>
+        <v>0.1248275537083323</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01422980003466152</v>
+        <v>0.08762875414237951</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01364211965267809</v>
+        <v>0.008405136815651868</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.06236177390650901</v>
+        <v>0.5749610267035563</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.007623674477425353</v>
+        <v>-0.08851841568271818</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.04314910863681892</v>
+        <v>-0.2354161283989495</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6363,25 +6363,25 @@
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03349466109785174</v>
+        <v>-0.271744317719762</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.001642604332717485</v>
+        <v>0.01787289100501106</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02679018920119219</v>
+        <v>0.1621219986726681</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,52 +6393,52 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.01068487401483509</v>
+        <v>-0.3313895214173477</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.004812318131834537</v>
+        <v>0.2045254549304195</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.00773204097683432</v>
+        <v>0.2209895469840183</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02662294950417437</v>
+        <v>-0.2622280135231328</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.004050833091589666</v>
+        <v>-0.02619707794799034</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.03148958583116034</v>
+        <v>0.145990169263627</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,19 +6447,19 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01270776701586833</v>
+        <v>-0.02411633408778911</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.009244334633828528</v>
+        <v>-0.097198369964515</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02386309733495847</v>
+        <v>0.004393797442896521</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,25 +6468,25 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.0139028280131466</v>
+        <v>-0.1415656467643779</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.03325284213609852</v>
+        <v>0.04651510064702103</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.001760983138845805</v>
+        <v>0.07146799158505118</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
@@ -6495,82 +6495,82 @@
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.02561566515131305</v>
+        <v>0.06521169383516764</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.008132986118546782</v>
+        <v>0.0718303687926589</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01216157183728593</v>
+        <v>-0.09638220654569717</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
         <v>-0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.02112845778588181</v>
+        <v>-0.07740638913994363</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.004993323280375564</v>
+        <v>-0.1172272062479303</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01109149501841999</v>
+        <v>0.05149142701540151</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.01221545924980194</v>
+        <v>-0.1044160848568333</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.009470151870062055</v>
+        <v>-0.06439763190413794</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01933533977152293</v>
+        <v>0.07717802694778664</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6579,37 +6579,37 @@
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02816804995451873</v>
+        <v>-0.2779415313241521</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.003760137488556624</v>
+        <v>-0.03851224234597674</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0321465888273262</v>
+        <v>0.1458007258636336</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.005018350660556292</v>
+        <v>-0.2656783557097271</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,25 +6618,25 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02431929299627959</v>
+        <v>0.04845104401291586</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03498763498465274</v>
+        <v>0.1490411647377692</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
         <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01010344927742902</v>
+        <v>-0.1132816062733676</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01003327465580131</v>
+        <v>-0.01810116167496266</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.00158408540320202</v>
+        <v>-0.009181095323911559</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.009082143176263317</v>
+        <v>-0.1130138037839584</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.04266018414259966</v>
+        <v>-0.01688202565603893</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,19 +6692,19 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5914379034894386</v>
+        <v>0.5213459946923387</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2700082841972247</v>
+        <v>-0.5876440515790818</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1764911818632713</v>
+        <v>0.03403124798268196</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6719,16 +6719,16 @@
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5000091316423384</v>
+        <v>0.5570118365202089</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2742230706801445</v>
+        <v>-0.7240001874509902</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.233142794411105</v>
+        <v>0.0466892917656741</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1149389259578944</v>
+        <v>0.1293772986206294</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.03452219132372505</v>
+        <v>-0.08010257937455502</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0489705818066543</v>
+        <v>-0.269033779713427</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,25 +6770,25 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2014803559320878</v>
+        <v>-0.03840870103263046</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.01027499409830972</v>
+        <v>-0.201399252978351</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.002996001515855707</v>
+        <v>-0.09735619526246123</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,49 +6797,49 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.03874974961562001</v>
+        <v>0.2122004082684252</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04304618538148554</v>
+        <v>-0.07795197761395199</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.1108289131866962</v>
+        <v>0.01935633613669566</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.6024871898722551</v>
+        <v>0.5358057565656539</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.08768800231804517</v>
+        <v>-0.2124109012166382</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.01297869914743469</v>
+        <v>-0.4044284458054129</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -6851,22 +6851,22 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.08808459700199292</v>
+        <v>-0.1158427986219762</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.09938598065545112</v>
+        <v>-0.2288235578301058</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1292167484824082</v>
+        <v>-0.003379850548471054</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
@@ -6881,16 +6881,16 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1517257483133761</v>
+        <v>0.1194422126903987</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.05971381048031623</v>
+        <v>0.1576271382550725</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1987674423509818</v>
+        <v>0.07908369681795943</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.3451021407812929</v>
+        <v>0.3520509075652952</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.08804673298095748</v>
+        <v>-0.2270736982898922</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.06692244169115173</v>
+        <v>-0.1864014906015671</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.120429673429857</v>
+        <v>-0.1653187179209645</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.03817396847238497</v>
+        <v>0.2830963244686239</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.01515397658264587</v>
+        <v>0.02541088251354555</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,16 +6962,16 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.1174312128646397</v>
+        <v>0.007890405595252378</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.05884056233782319</v>
+        <v>0.3103334966806593</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1405572483651377</v>
+        <v>0.2141191732075954</v>
       </c>
       <c r="CR12" t="n">
         <v>0</v>
@@ -6980,106 +6980,106 @@
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.104084178924646</v>
+        <v>-0.142876742848274</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.06199741040165992</v>
+        <v>0.3186302815248379</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.00561303817635082</v>
+        <v>0.03774897970685136</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.003951853314290088</v>
+        <v>-0.001250837582940084</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1435205245447175</v>
+        <v>0.07741210289289333</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01977365871526315</v>
+        <v>-0.007436910604353468</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06513249637737364</v>
+        <v>-0.2048884397127683</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.06954136876115312</v>
+        <v>0.1701180015124181</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.1232614574982204</v>
+        <v>0.01450372346255687</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.1369861246641911</v>
+        <v>-0.1304510365969281</v>
       </c>
       <c r="DY12" t="n">
         <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.04311834359862247</v>
+        <v>-0.07400628657783584</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.0716713096870663</v>
+        <v>-0.3191790808575856</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
@@ -7088,34 +7088,34 @@
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.09642902137969481</v>
+        <v>-0.06377401970498715</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.09893084267580986</v>
+        <v>0.229711153171288</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.1411487021733108</v>
+        <v>0.03939623364325966</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,19 +7124,19 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.09749976041729709</v>
+        <v>-0.1298469539032753</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03896866951435704</v>
+        <v>0.2255595309412923</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.07962980998225233</v>
+        <v>-0.06670960158777418</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7151,16 +7151,16 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1005016643008999</v>
+        <v>-0.172580073196615</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.06315332342626415</v>
+        <v>0.3032470749929617</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.03154279324818181</v>
+        <v>0.0140912479356247</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
@@ -7178,16 +7178,16 @@
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.1069053086129344</v>
+        <v>-0.1673211473222249</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.06192481393789113</v>
+        <v>0.1752878360226488</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.05721743776492584</v>
+        <v>-0.297674240629491</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,25 +7196,25 @@
         <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.01991874451372399</v>
+        <v>-0.02783883275826076</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.02731616210389017</v>
+        <v>-0.0389256338335229</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.05490476016112526</v>
+        <v>0.1150583475014462</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
@@ -7229,28 +7229,28 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.04095812196305167</v>
+        <v>-0.1773159011146321</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.04110984064748718</v>
+        <v>0.2979258277102511</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2345444383930769</v>
+        <v>0.2079083591319956</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -7267,52 +7267,52 @@
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1216807891449209</v>
+        <v>-0.3499032926907235</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1410537212993428</v>
+        <v>0.1666706192745256</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2381202740506073</v>
+        <v>0.1512621287183762</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.04539047436077651</v>
+        <v>-0.4576818751652462</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07194555998477496</v>
+        <v>0.09009356865678769</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03266054526219389</v>
+        <v>-0.01748441617990068</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -7321,40 +7321,40 @@
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06417996284898232</v>
+        <v>-0.04915178059616672</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04603389529523597</v>
+        <v>-0.1115062714598981</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.0271599026959527</v>
+        <v>0.05332743287235306</v>
       </c>
       <c r="AC13" t="n">
         <v>-0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.01199679884211743</v>
+        <v>0.07339483603320342</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.004159106550662947</v>
+        <v>0.2972934162772056</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -7363,49 +7363,49 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.001633980103269576</v>
+        <v>0.04952130307743747</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.01311220947692371</v>
+        <v>-0.174941332599824</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.06874272791987146</v>
+        <v>0.06636715067688802</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.1182004317564466</v>
+        <v>-0.1018137008292774</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.05074345304682504</v>
+        <v>-0.4291163026328818</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1528599084345949</v>
+        <v>-0.01228478540619437</v>
       </c>
       <c r="AY13" t="n">
         <v>-0</v>
@@ -7420,7 +7420,7 @@
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.1233976544867207</v>
+        <v>0.1787378557528227</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -7429,25 +7429,25 @@
         <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.01444688431409666</v>
+        <v>0.2651332275737766</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.08819682083908824</v>
+        <v>0.2673451717136184</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.02430412674535051</v>
+        <v>-0.03253233764945094</v>
       </c>
       <c r="BM13" t="n">
         <v>0</v>
@@ -7456,10 +7456,10 @@
         <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0152057089225464</v>
+        <v>0.008983739811534153</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.08150825544347831</v>
+        <v>-0.1054746689430155</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
@@ -7468,25 +7468,25 @@
         <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.05576673528481684</v>
+        <v>-0.08028872773838391</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0.003142789870127412</v>
+        <v>-0.3348626418168614</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.07638890276791373</v>
+        <v>-0.09246848750713178</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -7495,25 +7495,25 @@
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0.04347259515190958</v>
+        <v>-0.07524717488565219</v>
       </c>
       <c r="CE13" t="n">
         <v>0</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.01876570050951991</v>
+        <v>0.1271583817038271</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.02987607512746258</v>
+        <v>-0.05174231787945387</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
@@ -7528,46 +7528,46 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0.02310266060706646</v>
+        <v>0.03428015937008153</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.08804552791641454</v>
+        <v>0.1629107558446352</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.110088098134519</v>
+        <v>-0.1147411661900562</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0.03393015305738623</v>
+        <v>-0.06772979333070087</v>
       </c>
       <c r="CW13" t="n">
         <v>-0</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>-0.0008907786236073337</v>
+        <v>0.1304792609527434</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.02281371974151053</v>
+        <v>-0.03026245710573852</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
@@ -7582,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0.01644754394797067</v>
+        <v>-0.01964673972311087</v>
       </c>
       <c r="DF13" t="n">
         <v>-0</v>
@@ -7591,10 +7591,10 @@
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.05048212356975044</v>
+        <v>0.1437495314059382</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.02051766036843681</v>
+        <v>-0.01285244800883925</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
@@ -7609,79 +7609,79 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0.02722314561728139</v>
+        <v>-0.07075027911976285</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.04298152625656107</v>
+        <v>0.008520497641989255</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.0806404147873814</v>
+        <v>-0.01483392425628284</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0.03257304599443057</v>
+        <v>0.00859694863941275</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.02529879863495213</v>
+        <v>0.002137910895428038</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.02625557313327651</v>
+        <v>-0.01361573617140762</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0.04044317446478148</v>
+        <v>-0.1110719854965386</v>
       </c>
       <c r="EG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.007708190090731034</v>
+        <v>0.1084128961359276</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0003386619923779457</v>
+        <v>0.009499153532064153</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>0</v>
@@ -7690,22 +7690,22 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0.01321517887660108</v>
+        <v>0.03190706202787234</v>
       </c>
       <c r="EP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ13" t="n">
         <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.03128069370996575</v>
+        <v>0.1367378962626568</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.003428998992835393</v>
+        <v>0.0002351584173040033</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7717,19 +7717,19 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0.03639238685186365</v>
+        <v>-0.07551641174886968</v>
       </c>
       <c r="EY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.0113809565257668</v>
+        <v>0.1754251488090752</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.03716757278751184</v>
+        <v>-0.04401039010647084</v>
       </c>
       <c r="FC13" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.003017483390739973</v>
+        <v>0.05070744109078858</v>
       </c>
       <c r="FH13" t="n">
         <v>0</v>
@@ -7753,25 +7753,25 @@
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01287067936438947</v>
+        <v>0.1456576228319389</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.1174590351351823</v>
+        <v>0.1137154234995182</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
         <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.01251937648941016</v>
+        <v>-0.006206640936816864</v>
       </c>
       <c r="FQ13" t="n">
         <v>-0</v>
@@ -7780,49 +7780,49 @@
         <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.002720114583213521</v>
+        <v>0.2802908614473983</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.050405139684634</v>
+        <v>0.04190254829507001</v>
       </c>
       <c r="FU13" t="n">
         <v>0</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.02383870342904908</v>
+        <v>0.03622945125696433</v>
       </c>
       <c r="FZ13" t="n">
         <v>0</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.02429374442759327</v>
+        <v>0.2281280088114752</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
